--- a/case_studies/Free_MPW/2050/technologies.xlsx
+++ b/case_studies/Free_MPW/2050/technologies.xlsx
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2000</v>
+        <v>1188.23</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4.86</v>
+        <v>9.43</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -691,37 +691,37 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>114.1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>454.17</v>
+        <v>302.54</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>21.09</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>946.41</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>983.99</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>228.2</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>273.76</v>
+        <v>1526.74</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>36.8</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>22.37</v>
+        <v>1038.6</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>159.94</v>
@@ -730,10 +730,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>49.16</v>
+        <v>39.33</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>237.02</v>
+        <v>281.11</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1534.49</v>
+        <v>149.38</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>45.66</v>
@@ -779,22 +779,22 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>14.59</v>
+        <v>2.25</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>8.08</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>3.55</v>
+        <v>1.42</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>35.39</v>
+        <v>37.95</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>35.22</v>
+        <v>35.5</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>48.42</v>
+        <v>48.81</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -876,67 +876,67 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>94.33</v>
+        <v>12.17</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>7.07</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>176.52</v>
+        <v>6.39</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>663.88</v>
+        <v>153.06</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>54.33</v>
+        <v>25.09</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1369.36</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1502.3</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>607.9400000000001</v>
+        <v>31.96</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>643.22</v>
+        <v>2489.71</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>351.55</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>43.32</v>
+        <v>1706.72</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>260.55</v>
+        <v>231.42</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>14.73</v>
+        <v>0</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>348.55</v>
+        <v>0</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>611.7</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>27.91</v>
+        <v>34.5</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>0</v>
@@ -964,55 +964,55 @@
         <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>22.53</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>216.89</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>9.06</v>
+        <v>18.2</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>38.39</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>6.74</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>109.13</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>425.52</v>
+        <v>876.92</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>148.52</v>
+        <v>160.6</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>745.4</v>
+        <v>0</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>746.15</v>
+        <v>0</v>
       </c>
       <c r="O5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>131.18</v>
+        <v>20.11</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>131.18</v>
+        <v>1278.12</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>125.97</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>185.74</v>
+        <v>728.1</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>64.79000000000001</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>221.12</v>
+        <v>46.83</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1091,25 +1091,25 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>565.33</v>
+        <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>565.33</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>204.43</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>204.43</v>
+        <v>875.42</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>106.41</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0</v>
+        <v>595.53</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1121,10 +1121,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>106.41</v>
+        <v>0</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>361.56</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>0</v>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0</v>
+        <v>46.37</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0</v>
+        <v>3.96</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>48.52</v>
+        <v>19.41</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>0</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.57</v>
+        <v>22.58</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.8</v>
+        <v>39.41</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>1.43</v>
+        <v>2.19</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.18</v>
+        <v>22.31</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AA7" s="5" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>128.76</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>287.46</v>
+        <v>604.46</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1285,40 +1285,40 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>136.33</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>136.33</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>342.61</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>427.03</v>
+        <v>680.03</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>129.95</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>73.62</v>
+        <v>462.6</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>128.76</v>
+        <v>110.4</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>2.59</v>
+        <v>0.02</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>129.51</v>
+        <v>561.64</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>136.33</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>0</v>
